--- a/artfynd/A 61676-2025 artfynd.xlsx
+++ b/artfynd/A 61676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,123 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130798820</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövmyrbäcken, Lövmyrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577390</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7050146</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61676-2025 artfynd.xlsx
+++ b/artfynd/A 61676-2025 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>130798820</v>
       </c>
       <c r="B6" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61676-2025 artfynd.xlsx
+++ b/artfynd/A 61676-2025 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>130798820</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61676-2025 artfynd.xlsx
+++ b/artfynd/A 61676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>106576417</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577203.3504341017</v>
+        <v>577203</v>
       </c>
       <c r="R2" t="n">
-        <v>7050141.828870543</v>
+        <v>7050142</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106576824</v>
+        <v>106576488</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577268.4374914296</v>
+        <v>577226</v>
       </c>
       <c r="R3" t="n">
-        <v>7050052.937154705</v>
+        <v>7050090</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,19 +891,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106576488</v>
+        <v>106577833</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577226.0259658903</v>
+        <v>577310</v>
       </c>
       <c r="R4" t="n">
-        <v>7050090.235113067</v>
+        <v>7050004</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106577224</v>
+        <v>130798820</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +1010,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövmyrbäcken, Ång</t>
+          <t>Lövmyrbäcken, Lövmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577281.8381649702</v>
+        <v>577390</v>
       </c>
       <c r="R5" t="n">
-        <v>7050034.098305673</v>
+        <v>7050146</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1069,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130798820</v>
+        <v>106576824</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,42 +1127,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövmyrbäcken, Lövmyrbäcken, Ång</t>
+          <t>Lövmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577390</v>
+        <v>577268</v>
       </c>
       <c r="R6" t="n">
-        <v>7050146</v>
+        <v>7050052</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,27 +1182,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,6 +1221,114 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106577224</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövmyrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577282</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7050034</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61676-2025 artfynd.xlsx
+++ b/artfynd/A 61676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106576417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106576488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106577833</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130798820</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106576824</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,8 +1359,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106577224</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>